--- a/VitaStore/Task4/TCO.xlsx
+++ b/VitaStore/Task4/TCO.xlsx
@@ -704,14 +704,14 @@
       <c r="E3" s="8" t="n">
         <v>1000000</v>
       </c>
-      <c r="F3" s="8" t="n">
-        <v>6000000</v>
+      <c r="F3" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="8" t="n">
-        <v>6000000</v>
+      <c r="H3" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>11</v>
@@ -727,20 +727,20 @@
       <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>11</v>
+      <c r="D4" s="8" t="n">
+        <v>600000</v>
       </c>
       <c r="E4" s="8" t="n">
         <v>1500000</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>11</v>
+      <c r="F4" s="8" t="n">
+        <v>600000</v>
       </c>
       <c r="G4" s="8" t="n">
         <v>1500000</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>11</v>
+      <c r="H4" s="8" t="n">
+        <v>600000</v>
       </c>
       <c r="I4" s="8" t="n">
         <v>1500000</v>
@@ -986,7 +986,7 @@
       <c r="C13" s="15" t="s"/>
       <c r="D13" s="16" t="n">
         <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">SUM(D3:D9)</f>
-        <v>18500000</v>
+        <v>19100000</v>
       </c>
       <c r="E13" s="16" t="n">
         <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">SUM(E4:E10, E12)</f>
@@ -994,7 +994,7 @@
       </c>
       <c r="F13" s="16" t="n">
         <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">SUM(F3:F10, F12)</f>
-        <v>18500000</v>
+        <v>13100000</v>
       </c>
       <c r="G13" s="16" t="n">
         <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">SUM(G4:G10, G12)</f>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="H13" s="16" t="n">
         <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">SUM(H3:H10, H12)</f>
-        <v>18500000</v>
+        <v>13100000</v>
       </c>
       <c r="I13" s="16" t="n">
         <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">SUM(I4:I10, I12)</f>
@@ -1017,7 +1017,7 @@
       <c r="C14" s="18" t="s"/>
       <c r="D14" s="19" t="n">
         <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">SUM(D3:D12)</f>
-        <v>18500000</v>
+        <v>19100000</v>
       </c>
       <c r="E14" s="19" t="n">
         <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">SUM(E3:E12)</f>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="F14" s="19" t="n">
         <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">SUM(F3:F12)</f>
-        <v>18500000</v>
+        <v>13100000</v>
       </c>
       <c r="G14" s="19" t="n">
         <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">SUM(G3:G12)</f>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="H14" s="19" t="n">
         <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">SUM(H3:H12)</f>
-        <v>18500000</v>
+        <v>13100000</v>
       </c>
       <c r="I14" s="19" t="n">
         <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">SUM(I3:I12)</f>
